--- a/artfynd/A 41173-2026 artfynd.xlsx
+++ b/artfynd/A 41173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137248444</v>
       </c>
       <c r="B2" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41173-2026 artfynd.xlsx
+++ b/artfynd/A 41173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137248444</v>
       </c>
       <c r="B2" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41173-2026 artfynd.xlsx
+++ b/artfynd/A 41173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137248444</v>
       </c>
       <c r="B2" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41173-2026 artfynd.xlsx
+++ b/artfynd/A 41173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137248444</v>
       </c>
       <c r="B2" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41173-2026 artfynd.xlsx
+++ b/artfynd/A 41173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137248444</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41173-2026 artfynd.xlsx
+++ b/artfynd/A 41173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137248444</v>
       </c>
       <c r="B2" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41173-2026 artfynd.xlsx
+++ b/artfynd/A 41173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137248444</v>
       </c>
       <c r="B2" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41173-2026 artfynd.xlsx
+++ b/artfynd/A 41173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137248444</v>
       </c>
       <c r="B2" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41173-2026 artfynd.xlsx
+++ b/artfynd/A 41173-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137248444</v>
       </c>
       <c r="B2" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
